--- a/Database/deseases.xlsx
+++ b/Database/deseases.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antipozitife/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antipozitife/Desktop/sealara/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918A5CB6-CF18-6642-8E9B-A00BBD1A8D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCE16DB-251D-7145-96A8-DEE0FD2B7D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{FFCC9D57-F35F-E246-9B37-28BBBD85C62B}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{FFCC9D57-F35F-E246-9B37-28BBBD85C62B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="536">
   <si>
     <t>№</t>
   </si>
@@ -3047,12 +3047,21 @@
   <si>
     <t>Глобально (повсеместно) | Восточная Европа и СНГ (Россия, Беларусь, Казахстан) | Северная и Центральная Европа | Северная Америка | Центральная Азия</t>
   </si>
+  <si>
+    <t>картинка</t>
+  </si>
+  <si>
+    <t>https://www.smclinic.ru/upload/iblock/c6f/1uz4ysvcc7q6s5x9wk78mmy7lky1027n.jpg.webp</t>
+  </si>
+  <si>
+    <t>https://www.smclinic.ru/upload/iblock/0a5/1fuyi6hi70ieaao7xb2frk7i9sdpdexk.jpg.webp</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3078,6 +3087,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3096,10 +3113,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -3113,14 +3131,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3453,7 +3469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9421AA35-C797-EB48-B98A-18AB923DBDE8}">
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
@@ -3470,7 +3486,7 @@
     <col min="15" max="15" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="38" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="38" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3516,8 +3532,11 @@
       <c r="O1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>533</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3563,8 +3582,11 @@
       <c r="O2" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="P2" s="5" t="s">
+        <v>534</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f>A2 + 1</f>
         <v>2</v>
@@ -3611,8 +3633,11 @@
       <c r="O3" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="P3" s="5" t="s">
+        <v>535</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A48" si="0">A3 + 1</f>
         <v>3</v>
@@ -3656,11 +3681,11 @@
       <c r="N4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3668,7 +3693,7 @@
       <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -3695,20 +3720,20 @@
       <c r="K5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3716,7 +3741,7 @@
       <c r="B6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -3743,20 +3768,20 @@
       <c r="K6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3764,7 +3789,7 @@
       <c r="B7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -3791,20 +3816,20 @@
       <c r="K7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3812,7 +3837,7 @@
       <c r="B8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -3839,20 +3864,20 @@
       <c r="K8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="1" t="s">
         <v>84</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3860,7 +3885,7 @@
       <c r="B9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -3887,20 +3912,20 @@
       <c r="K9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3908,7 +3933,7 @@
       <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -3935,20 +3960,20 @@
       <c r="K10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="O10" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3956,7 +3981,7 @@
       <c r="B11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -3983,20 +4008,20 @@
       <c r="K11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="O11" s="5" t="s">
+      <c r="O11" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -4004,7 +4029,7 @@
       <c r="B12" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -4034,17 +4059,17 @@
       <c r="L12" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="O12" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -4092,7 +4117,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -4140,7 +4165,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -4188,7 +4213,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -5767,6 +5792,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="P2" r:id="rId1" xr:uid="{CF71BBC1-C361-B04C-8EE0-74236E89983D}"/>
+    <hyperlink ref="P3" r:id="rId2" xr:uid="{ED3922B6-7AEF-EB4A-9FCC-7F77BF01BB7E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Database/deseases.xlsx
+++ b/Database/deseases.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antipozitife/Desktop/sealara/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCE16DB-251D-7145-96A8-DEE0FD2B7D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D14E7CD-F7B6-D248-89FC-AF8606102210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{FFCC9D57-F35F-E246-9B37-28BBBD85C62B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{FFCC9D57-F35F-E246-9B37-28BBBD85C62B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="596">
   <si>
     <t>№</t>
   </si>
@@ -58,14 +59,6 @@
   </si>
   <si>
     <t>о заболевании</t>
-  </si>
-  <si>
-    <t>Причиной заболевания является золотистый стафилококк. Патологический процесс обычно развивается в большеберцовой кости, которая прилежит к коленному суставу. Абсцесс также может быть локализован и в других длинных трубчатых костях.
-Заболевание проявляется периодически возникающей болью, которая обычно появляется ночью, после физических нагрузок, а также проявляет метеозависимость. На фоне хронического процесса наблюдается утолщение кости в зоне поражения. Для абсцесса Броди характерна системная реакция организма с повышением температуры тела. Однако у некоторых пациентов возможно латентное клиническое развитие, и первые признаки выявляются при проведении рентгенологического обследования. На рентгенограммах определяется очаг просветления, при вскрытии которого выделяется гной.
-Основной вид лечения – хирургический. Врач вскрывает кость, удаляет омертвевшие ткани, выскабливает внутреннюю стенку полости, тампонирует и зашивает рану.</t>
-  </si>
-  <si>
-    <t>периодические боли в пораженной кости | утолщение пораженной кости | усиление болевых ощущений в ночное время и при перемене погоды | покраснение кожи над очагом хронического воспаления (непостоянный признак) | подъем температуры тела (непостоянный признак) | повышение температуры тела | озноб</t>
   </si>
   <si>
     <t>причины</t>
@@ -103,10 +96,6 @@
     <t>реабилитация</t>
   </si>
   <si>
-    <t>После хирургического лечения накладывается гипсовая повязка сроком на 1 месяц. Это позволяет создать оптимальные условия для заживления костного дефекта. Для ускорения восстановительных процессов рекомендуется курс физиопроцедур.
-В послеоперационном периоде проводятся регулярные обработки операционной раны, продолжается антибактериальная терапия.</t>
-  </si>
-  <si>
     <t>специалист</t>
   </si>
   <si>
@@ -126,9 +115,6 @@
   </si>
   <si>
     <t>лабораторные показатели</t>
-  </si>
-  <si>
-    <t>повышение лейкоцитов | повышение СОЭ | повышение уровня С-реактивного белка (СРБ) | наличие золотистого стафилококкока</t>
   </si>
   <si>
     <t>мужской</t>
@@ -143,9 +129,6 @@
     <t>Абсцессы могут образоваться в любой анатомической области. Особенно часто они встречаются на ягодицах, бедре, плече, на передней брюшной стенке, то есть в тех зонах, где имеется обилие подкожно-жировой прослойки. Гнойники могут образоваться и между мышечными пластами, что определяет выраженность местных симптомов.
 Диагностика заболевания не вызывает затруднений. Диагностический поиск базируется на оценке клинических проявлений, визуальном осмотре и пальпации. Дополнительное обследование помогает оценить ответ организма на воспалительный процесс.
 Лечение абсцесса обязательно предполагает вскрытие гнойного очага, его обработку и дренирование. Консервативная терапия дополняет хирургическое вмешательство.</t>
-  </si>
-  <si>
-    <t>Покраснение кожи над патологической зоной | Локальное повышение кожной температуры | Отечность тканей | Нарушение функции пораженной области | Боль</t>
   </si>
   <si>
     <t>Непосредственная причина абсцесса мягких тканей – это проникновение гноеродных бактерий в кожу, подкожно-жировой или мышечный слой. Бактериальная флора приводит к развитию инфекционного воспаления, которое из экссудативной стадии достаточно быстро переходит в гнойную с лизисом пораженных тканей.
@@ -165,21 +148,6 @@
 Для оценки системного ответа организма проводится общеклинический анализ крови и мочи, биохимический тест крови и другие исследования (по показаниям).</t>
   </si>
   <si>
-    <t xml:space="preserve">Согласно клиническим рекомендациям, лечение абсцесса мягких тканей проводится только хирургическим способом, т.к. гною важно создать отток, чтобы он не распространился во внутренние среды организма.
-Консервативное лечение
-При обширных абсцессах, когда имеется интоксикационный синдром, проводится комплексная терапия, которая направлена на восстановление функционального состояния организма. Основными направлениями консервативного лечения являются:
-антибактериальное (назначаются системные антибиотики);
-противовоспалительное;
-жаропонижающее;
-дезинтоксикационное;
-обезболивающее.
-Однако консервативная терапия будет неэффективной без хирургического лечения гнойника.
-Хирургическое лечение
-Наиболее распространенный вариант хирургического вмешательства при абсцессе мягких тканей – это вскрытие, промывание гнойной полости антисептиками и ее последующее дренирование, которое позволит обеспечить наиболее полное очищение раны. В некоторых случаях может применяться пункционный способ, но иногда образованное отверстие закрывается преждевременно, что снижает эффективность методики.
-Для лучшего восстановления тканей рекомендуется регулярно проводить обработки раны с использованием антисептических растворов. Обработки проводят до тех пор, пока не появятся здоровые грануляции, которые являются признаком нормально протекающего репаративного процесса.
-</t>
-  </si>
-  <si>
     <t>Основными направлениями профилактики гнойных образований мягких тканей являются:
 своевременное лечение очагов хронической инфекции;
 своевременная обработка повреждений кожного покрова;
@@ -195,9 +163,6 @@
     <t>хирург | травматолог-ортопед</t>
   </si>
   <si>
-    <t>0-100</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -209,9 +174,6 @@
   <si>
     <t>Абсцесс печени – редкая патология, заболеваемость которой составляет около 3.6 на 100 тысяч населения ежегодно. Страдают преимущественно пациенты зрелого и пожилого возраста, мужчины несколько чаще женщин.
 Локализация некоторых абсцессов значительно затрудняет диагностику, что обусловливает позднюю постановку диагноза и развитие осложнений.</t>
-  </si>
-  <si>
-    <t>тяжесть в правом подреберье | боль тупого или ноющего характера, иррадиирующих в плечо или правую лопатку | Интенсивность болей возрастает в положении на левом боку, а на правом, напротив, снижается, особенно с коленями, подтянутыми к груди | повышение температуры тела до фебрильных (38-39°С) значений, сопровождающееся ознобом | общая слабость, недомогание, быстрая утомляемость | одышка, затрудненное дыхание, кашель, дискомфорт, тяжесть, боль в нижней части грудной клетки справа | тошнота, рвота | снижение массы тела | расстройства стула (диарея) | отсутствие аппетита | выраженная потливость, особенно ночью | болезненность при пальпации (прощупывании) живота в области правого подреберья, в проекции абсцесса | хрипы в нижнем отделе правого легкого | увеличение печени | приподнятый купол диафрагмы справа | пожелтение кожи, видимых слизистых оболочек, склер</t>
   </si>
   <si>
     <t>Наиболее часто абсцесс осложняет течение аппендицита, желчнокаменной болезни, сепсиса, развиваясь вторично на их фоне при отсутствии своевременного лечения.
@@ -244,16 +206,6 @@
   </si>
   <si>
     <t>гастроэнтеролог | гепатолог | инфекционист | хирург</t>
-  </si>
-  <si>
-    <t xml:space="preserve">повышение лейкоцитов | увеличение молодых форм нейтрофилов | повышение СОЭ | повышение уровня С-реактивного белка (СРБ) | повышение глюкозы крови
-</t>
-  </si>
-  <si>
-    <t>повышение лейкоцитов | увеличение палочкоядерных нейтрофилов | повышение СОЭ | снижение гемоглобина | снижение эритроцитов | снижение тромбоцитов | повышение тромбоцитов | повышение щелочной фосфатазы | повышение АЛТ | повышение АСТ | повышение общего билирубина | повышение С-реактивного белка (СРБ) | повышение прокальцитонина | снижение альбумина | увеличение протромбинового времени | положительный посев крови | положительные антиамебные антитела</t>
-  </si>
-  <si>
-    <t>50-100</t>
   </si>
   <si>
     <t>Авитаминоз (дефицит А)</t>
@@ -310,20 +262,6 @@
 Тактика лечения авитаминоза определяется симптомами заболевания, состоянием пациента и формой патологии.</t>
   </si>
   <si>
-    <t xml:space="preserve">Основа профилактики авитаминоза – сбалансированное и рациональное питание. Необходимо отказаться от строгих диет и питаться разнообразно, включая в ежедневный рацион:
-нежирные сорта мяса и рыбы;
-молочные и кисломолочные продукты;
-твердые сыры;
-свежие плоды и зелень;
-крупы;
-морепродукты;
-яйца;
-орехи и сухофрукты;
-сливочное и растительное масло.
-Желательно максимально ограничить блюда фаст-фуда, продукты быстрого приготовления, алкоголь. Также стоит придерживаться активного образа жизни, не заниматься самолечением и регулярно проходить профилактические обследования со сдачей необходимых анализов.
-</t>
-  </si>
-  <si>
     <t>Авитаминоз (дефицит D)</t>
   </si>
   <si>
@@ -340,27 +278,6 @@
   </si>
   <si>
     <t>Авитаминоз (дефицит B)</t>
-  </si>
-  <si>
-    <t>повышенная утомляемость | апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | снижение работоспособности | сухость и покраснение кожи | истончение, ломкость и выпадение волос | кожный зуд | расслаивание и хрупкость ногтевых пластин | появление шелушений, трещин на лице и теле | снижение или полная потеря обоняния | снижение или полная потеря вкусового восприятия | приступы отвращения к еде | тошнота после приемов пищи | синдром «куриной слепоты», когда человек в сумерках или темноте очень плохо видит | нарушение фертильности | развитие анемии | развитие мочекаменной болезни | ослабление иммунитета</t>
-  </si>
-  <si>
-    <t>повышенная утомляемость | апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | снижение работоспособности | мышечные, суставные и костные боли | частые переломы, которые долго заживают | нарушения координации и походки | судороги в мышцах, особенно в ночное время | неврологические признаки | истончение эмали зубов | очаговое выпадение волос на голове и теле | ослабление иммунитета</t>
-  </si>
-  <si>
-    <t>повышенная утомляемость | апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | снижение работоспособности | снижение половой функции | мышечная слабость и судороги, особенно в руках и ногах | повышенная утомляемость | спазмы мышц | ослабление иммунитета</t>
-  </si>
-  <si>
-    <t>повышенная утомляемость | апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | снижение работоспособности | регулярные самопроизвольные прерывания беременности | мышечная слабость и судороги, особенно в руках и ногах | повышенная утомляемость | спазмы мышц | ослабление иммунитета</t>
-  </si>
-  <si>
-    <t>повышенная утомляемость | апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | снижение работоспособности | спонтанные кровотечения | носовые кровотечения, которые возникают на фоне физической нагрузки | носовые кровотечения, которые возникают на фоне эмоционального переживания | носовые кровотечения | легочные и желудочные кровотечения | кровоизлияния в суставные полости | даже от малейшего давления возникают многочисленные синяки на лице и теле | ослабление иммунитета</t>
-  </si>
-  <si>
-    <t>повышенная утомляемость | апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | снижение работоспособности | цинга | десны сильно кровоточат | выпадение зубов | поражение сердечно-сосудистой системы и почек | кровоизлияние в мягкие ткани | ослабление иммунитета</t>
-  </si>
-  <si>
-    <t>повышенная утомляемость | апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | снижение работоспособности | ослабление иммунитета | постоянная одышка | судороги в икроножных мышцах, особенно после ходьбы, бега, физических упражнений | снижение чувствительности в стопах и пальцах ног | расстройства аппетита и стула | частые головные боли | появление трещин в уголках рта | отечность, ощущения зуда и жжения на языке | снижение выносливости | головокружение | шелушение кожи на лице и теле | нарушения зрения | учащенный пульс и громкое, отчетливое сердцебиение | поражение периферическая нервная система | гепатомегалия | атрофические изменения в слизистых тканях органов пищеварения | недержание мочи и каловых масс</t>
   </si>
   <si>
     <t>Агалактия</t>
@@ -450,9 +367,6 @@
     <t>акушер-гинеколог | педиатр</t>
   </si>
   <si>
-    <t>снижение уровня витамина А (ретинола) в сыворотке крови (&lt;0,35 мкмоль/л — острый дефицит, 0,7–1,22 мкмоль/л — начальная недостаточность) | Снижение ретинол-связывающего белка (РСБ) | снижение уровня цинка | признаки анемии (снижение гемоглобина и эритроцитов) |  Часто выявляет признаки анемии (снижение гемоглобина и эритроцитов), а также возможны признаки хронического воспаления или иммунодефицита (изменение лейкоцитарной формулы)</t>
-  </si>
-  <si>
     <t>терапевт | педиатр</t>
   </si>
   <si>
@@ -465,9 +379,6 @@
     <t>Восточной Азии | Юго-Восточной Азии</t>
   </si>
   <si>
-    <t xml:space="preserve">Низкий уровень цианокобаламина (B12) | Низкий уровень фолиевой кислоты (B9) | Повышение среднего объема эритроцитов (MCV), снижение гемоглобина (Hb) и эритроцитов | Снижение уровня лейкоцитов и тромбоцитов при тяжелом дефиците </t>
-  </si>
-  <si>
     <t xml:space="preserve">мужской </t>
   </si>
   <si>
@@ -478,21 +389,6 @@
   </si>
   <si>
     <t>Северная Африка | Ближний Восток | Южная Азия | Тропическая Африка | Латинская Америка | Юго-Восточная Азия</t>
-  </si>
-  <si>
-    <t>Низкий уровень альфа-токоферола в плазме | Повышение уровня непрямого билирубина и лактатдегидрогеназы (ЛДГ) | Снижение гемоглобина (Hb) и эритроцитов при гемолитической анемии, повышение ретикулоцитов | Снижение соотношения витамина Е к общему количеству липидов сыворотки (менее 0,8 мг/г)</t>
-  </si>
-  <si>
-    <t>Низкий уровень филлохинона в плазме | Увеличение протромбинового времени (ПВ) и международного нормализованного отношения (МНО) | Повышение уровня неактивного протромбина (PIVKA-II) | Увеличение активированного частичного тромбопластинового времени (АЧТВ) при выраженном дефиците</t>
-  </si>
-  <si>
-    <t>Низкий уровень аскорбиновой кислоты в плазме или лейкоцитах | Снижение гемоглобина (Hb) и эритроцитов (из-за нарушения всасывания железа и кровопотерь) | Увеличение времени кровотечения при нормальных показателях свертываемости (ПВ, АЧТВ) | Снижение уровня альбумина и гипохолестеринемия при длительном течении</t>
-  </si>
-  <si>
-    <t>Низкий уровень тиаминпирофосфата в цельной крови | Повышение уровня пирувата и лактата в плазме | Снижение активности транскетолазы эритроцитов | Низкий уровень пиридоксаль-5-фосфата (ПЛФ) в плазме | Повышение уровня гомоцистеина в крови | Снижение гемоглобина (Hb) и микроцитоз (низкий MCV) в общем анализе крови | Низкий уровень цианокобаламина и голотранскобаламина | Повышение уровня метилмалоновой кислоты (ММА) и гомоцистеина | Повышение среднего объема эритроцитов (MCV), снижение гемоглобина и эритроцитов | Низкий уровень фолатов в плазме и эритроцитах | Повышение уровня гомоцистеина | Макроцитоз (повышение MCV) и гиперхромия эритроцитов</t>
-  </si>
-  <si>
-    <t>Низкий уровень пролактина в сыворотке крови | Повышение уровня прогестерона (при задержке частей плаценты) | Снижение уровня гормонов щитовидной железы (Т3, Т4) при эндокринных причинах | Низкий уровень эстрадиола и кортизола при подозрении на синдром Шихана</t>
   </si>
   <si>
     <t>0 - 1</t>
@@ -557,25 +453,6 @@
 анализ биоэлектрической активности коры для оценки ее функционального состояния;
 дополнительные лабораторные исследования при предположении обменных или воспалительных нарушений.
 Оценка состояния пациента при агнозии требует наблюдения в динамике. Следует учитывать, что у одного человека могут одновременно присутствовать несколько форм нарушения узнавания, например сочетание зрительной и речевой слуховой агнозии. Четкое определение характера и объема расстройства позволяет сформировать персонализированную стратегию лечения и последующей реабилитации.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Лечение агнозии направлено на восстановление нарушенного взаимодействия между восприятием и его осмыслением. Основная задача терапии — помочь мозгу заново выстроить утраченные связи, частично компенсировать дефект и снизить риск дальнейшего повреждения корковых структур. Выбор лечебной стратегии всегда индивидуален и зависит от причины возникновения расстройства, его клинической формы и общего функционального состояния пациента. На практике чаще всего применяется сочетание медикаментозных и немедикаментозных методов воздействия.
-Фармакологическая поддержка подбирается с учетом ведущих механизмов поражения и может включать следующие группы средств:
-препараты, способствующие улучшению кровоснабжения мозговой ткани и доставки кислорода;
-средства, поддерживающие энергетические и обменные процессы в нейронах;
-препараты с защитным действием в отношении нервных клеток;
-средства, влияющие на передачу сигналов между нейронами и повышающие адаптационные возможности мозга;
-противовоспалительные и противоотечные средства в случаях, когда расстройство обусловлено активным повреждающим процессом.
-Медикаментозная терапия создает благоприятный фон для восстановления функций коры и помогает замедлить развитие структурных и функциональных изменений.
-Ведущее значение в коррекции агнозии принадлежит немедикаментозным методам, направленным на активную перестройку познавательных процессов. В программу лечения могут входить:
-системная нейропсихологическая работа с акцентом на тренировку нарушенных механизмов узнавания;
-упражнения, развивающие зрительное, слуховое и тактильное восприятие;
-логопедическая коррекция при нарушениях понимания речи и звуков;
-когнитивные занятия, направленные на улучшение анализа и интерпретации информации;
-обучение адаптивным стратегиям, облегчающим повседневную деятельность;
-психотерапевтическая поддержка, помогающая снизить тревожность и повысить мотивацию к лечению.
-Комплексное воздействие позволяет задействовать компенсаторные ресурсы мозга и способствует формированию новых функциональных связей. Результативность лечения во многом определяется регулярностью занятий и активным участием самого пациента в процессе восстановления.
-</t>
   </si>
   <si>
     <t>Предупреждение развития агнозии связано прежде всего с сохранением здоровья корковых структур и поддержанием полноценной работы познавательных процессов. Поскольку нарушение узнавания, как правило, формируется не само по себе, а на фоне других заболеваний или повреждений мозга, особое значение приобретает управление факторами, способными негативно повлиять на состояние нервной системы.
@@ -615,13 +492,7 @@
     <t>Глобально (повсеместно) | Регионы с высокой долей пожилого населения (Европа, Северная Америка, Восточная Азия) | Страны с высоким уровнем сердечно-сосудистых заболеваний (Восточная Европа, СНГ, Центральная Азия)</t>
   </si>
   <si>
-    <t>Низкий уровень глюкозы или электролитный дисбаланс (при метаболической этиологии) | Маркеры нейродегенерации (тау-белок, амилоид) в ликворе | Изменения на МРТ/КТ (атрофия зон коры, ишемия, гематомы) | Снижение перфузии в специфических отделах мозга при ОФЭКТ или ПЭТ</t>
-  </si>
-  <si>
     <t>Агранулоцитоз</t>
-  </si>
-  <si>
-    <t>Снижение количества лейкоцитов (менее 1,0×10⁹/л) | Снижение абсолютного числа нейтрофилов (менее 0,5×10⁹/л) | Отсутствие или резкое снижение молодых форм нейтрофилов в лейкоцитарной формуле | Относительный лимфоцитоз при нормальном или незначительно сниженном уровне тромбоцитов и эритроцитов</t>
   </si>
   <si>
     <t>Агранулоцитоз — это тяжелое гематологическое состояние, характеризующееся резким снижением или почти полным исчезновением гранулоцитов в периферической крови. В первую очередь речь идет о нейтрофилах — клетках, которые формируют основу врожденной защиты организма от инфекций. Когда их количество падает ниже критического уровня (менее 0,5 × 10⁹/л, а при тяжелом течении — менее 0,2 × 10⁹/л), иммунная система утрачивает способность адекватно реагировать даже на минимальное микробное воздействие.
@@ -633,9 +504,6 @@
 В дальнейшем существенный вклад в изучение заболевания внесли немецкий гематолог Вернер Шульц и французский исследователь Жорж Видаль, которые предложили рассматривать агранулоцитоз как отдельный синдром, а не как случайную лабораторную находку. В этот период появилось понимание того, что снижение гранулоцитов может быть обусловлено как повреждением костного мозга, так и иммунными механизмами.
 Во второй половине XX века, с ростом фармакотерапии, внимание исследователей сместилось в сторону лекарственного агранулоцитоза. Было установлено, что ряд препаратов способен вызывать либо прямое токсическое угнетение миелопоэза, либо запускать иммунные реакции с разрушением нейтрофилов. Эти наблюдения легли в основу современных классификаций, выделяющих миелотоксический, иммунный и гаптеновый агранулоцитоз.
 Современные клинические рекомендации опираются на накопленные данные экспериментальной гематологии, иммунологии и фармакологии. Они основаны на лучших мировых достижениях. Внедрение современных клинических рекомендаций по агранулоцитозу позволило значительно снизить смертность (при своевременной диагностике и лечении).</t>
-  </si>
-  <si>
-    <t>резкое снижение защитных возможностей организма | общее состояние ухудшается в течение нескольких часов или дней | Температурная реакция | повышение температуры тела до высоких цифр без очевидного очага инфекции | язвенно-некротические изменения слизистой оболочки полости рта | боли при глотании, иррадиирующие в уши | признаки интоксикации, не соответствующие локальным проявлениям | озноб, выраженную слабость, резкое снижение работоспособности | воспаление десен с кровоточивостью и неприятным запахом | воспалительные изменения кожи и подкожной клетчатки | боль в горле, затруднение глотания, ощущение жжения в ротоглотке | появление налетов серо-зеленого цвета на миндалинах | склонность к быстрому распространению инфекционных процессов</t>
   </si>
   <si>
     <t>Агранулоцитоз не возникает спонтанно. В его основе всегда лежит воздействие факторов, нарушающих образование или выживание гранулоцитов. Эти механизмы могут быть прямыми, когда страдает костномозговое кроветворение, или опосредованными — через иммунные реакции. В клинической практике агранулоцитоз нередко развивается как осложнение другого заболевания или как ответ организма на внешнее вмешательство.
@@ -3056,12 +2924,321 @@
   <si>
     <t>https://www.smclinic.ru/upload/iblock/0a5/1fuyi6hi70ieaao7xb2frk7i9sdpdexk.jpg.webp</t>
   </si>
+  <si>
+    <t>распространенность</t>
+  </si>
+  <si>
+    <t>изменения на теле</t>
+  </si>
+  <si>
+    <t>И видимые, и внутренние</t>
+  </si>
+  <si>
+    <t>время начала симптомов</t>
+  </si>
+  <si>
+    <t>Постепенно (за недели или месяцы)</t>
+  </si>
+  <si>
+    <t>интенсивность ощущений</t>
+  </si>
+  <si>
+    <t>Ощущения сильные, явные</t>
+  </si>
+  <si>
+    <t>частота симптомов</t>
+  </si>
+  <si>
+    <t>Постоянные</t>
+  </si>
+  <si>
+    <t>повышение температуры тела</t>
+  </si>
+  <si>
+    <t>Высокая (38°C и выше)</t>
+  </si>
+  <si>
+    <t>наличие слабости, усталости или снижения работоспособности</t>
+  </si>
+  <si>
+    <t>Выраженная</t>
+  </si>
+  <si>
+    <t>связь симптомов с чем-то</t>
+  </si>
+  <si>
+    <t>Да, есть связь</t>
+  </si>
+  <si>
+    <t>характер боли</t>
+  </si>
+  <si>
+    <t>проблемы систем организма</t>
+  </si>
+  <si>
+    <t>Суставы</t>
+  </si>
+  <si>
+    <t>Пульсирующая: Связана с воспалением или нарушением кровообращения</t>
+  </si>
+  <si>
+    <t>прогрессирование болезни</t>
+  </si>
+  <si>
+    <t>Примерно одинаково</t>
+  </si>
+  <si>
+    <t>общий анализ крови</t>
+  </si>
+  <si>
+    <t>биохимический анализ крови</t>
+  </si>
+  <si>
+    <t>бактериологический анализ</t>
+  </si>
+  <si>
+    <t>повышение лейкоцитов | повышение СОЭ</t>
+  </si>
+  <si>
+    <t>повышение уровня С-реактивного белка (СРБ)</t>
+  </si>
+  <si>
+    <t>периодические боли в пораженной кости | утолщение пораженной кости | усиление болевых ощущений в ночное время и при перемене погоды | покраснение кожи над очагом хронического воспаления (непостоянный признак) | озноб</t>
+  </si>
+  <si>
+    <t>"Причиной заболевания является золотистый стафилококк. Патологический процесс обычно развивается в большеберцовой кости, которая прилежит к коленному суставу. Абсцесс также может быть локализован и в других длинных трубчатых костях.
+Заболевание проявляется периодически возникающей болью, которая обычно появляется ночью, после физических нагрузок, а также проявляет метеозависимость. На фоне хронического процесса наблюдается утолщение кости в зоне поражения. Для абсцесса Броди характерна системная реакция организма с повышением температуры тела. Однако у некоторых пациентов возможно латентное клиническое развитие, и первые признаки выявляются при проведении рентгенологического обследования. На рентгенограммах определяется очаг просветления, при вскрытии которого выделяется гной.
+Основной вид лечения – хирургический. Врач вскрывает кость, удаляет омертвевшие ткани, выскабливает внутреннюю стенку полости, тампонирует и зашивает рану."</t>
+  </si>
+  <si>
+    <t>"После хирургического лечения накладывается гипсовая повязка сроком на 1 месяц. Это позволяет создать оптимальные условия для заживления костного дефекта. Для ускорения восстановительных процессов рекомендуется курс физиопроцедур.
+В послеоперационном периоде проводятся регулярные обработки операционной раны, продолжается антибактериальная терапия."</t>
+  </si>
+  <si>
+    <t>территория</t>
+  </si>
+  <si>
+    <t>2.5%</t>
+  </si>
+  <si>
+    <t>Внезапно (за часы или 1-2 дня)</t>
+  </si>
+  <si>
+    <t>Лёгкая</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>Стало хуже</t>
+  </si>
+  <si>
+    <t>повышение лейкоцитов | повышение СОЭ | увеличение молодых форм нейтрофилов</t>
+  </si>
+  <si>
+    <t>повышение уровня С-реактивного белка (СРБ) | повышение глюкозы</t>
+  </si>
+  <si>
+    <t>покраснение кожи над патологической зоной | локальное повышение кожной температуры | отечность тканей | нарушение функции пораженной области | боль</t>
+  </si>
+  <si>
+    <t>Согласно клиническим рекомендациям, лечение абсцесса мягких тканей проводится только хирургическим способом, т.к. гною важно создать отток, чтобы он не распространился во внутренние среды организма.
+Консервативное лечение
+При обширных абсцессах, когда имеется интоксикационный синдром, проводится комплексная терапия, которая направлена на восстановление функционального состояния организма. Основными направлениями консервативного лечения являются:
+антибактериальное (назначаются системные антибиотики);
+противовоспалительное;
+жаропонижающее;
+дезинтоксикационное;
+обезболивающее.
+Однако консервативная терапия будет неэффективной без хирургического лечения гнойника.
+Хирургическое лечение
+Наиболее распространенный вариант хирургического вмешательства при абсцессе мягких тканей – это вскрытие, промывание гнойной полости антисептиками и ее последующее дренирование, которое позволит обеспечить наиболее полное очищение раны. В некоторых случаях может применяться пункционный способ, но иногда образованное отверстие закрывается преждевременно, что снижает эффективность методики.
+Для лучшего восстановления тканей рекомендуется регулярно проводить обработки раны с использованием антисептических растворов. Обработки проводят до тех пор, пока не появятся здоровые грануляции, которые являются признаком нормально протекающего репаративного процесса.</t>
+  </si>
+  <si>
+    <t>Юго-Восточная Азия (Таиланд) | Северная Америка (США) | Европа (Великобритания, Румыния, Португалия, Греция) | Океания (Фиджи)</t>
+  </si>
+  <si>
+    <t>Пищеварительная (тошнота, боли в животе)</t>
+  </si>
+  <si>
+    <t>повышение лейкоцитов, увеличение палочкоядерных нейтрофилов, повышение СОЭ, снижение гемоглобина, снижение эритроцитов, снижение тромбоцитов</t>
+  </si>
+  <si>
+    <t>повышение тромбоцитов (вторичный тромбоцитоз), повышение щелочной фосфатазы, повышение АЛТ, повышение АСТ, повышение общего билирубина, повышение С-реактивного белка (СРБ), повышение глюкозы</t>
+  </si>
+  <si>
+    <t>тяжесть в правом подреберье | боль тупого или ноющего характера, иррадиирующих в плечо или правую лопатку | Интенсивность болей возрастает в положении на левом боку, а на правом, напротив, снижается, особенно с коленями, подтянутыми к груди | одышка, затрудненное дыхание, кашель, дискомфорт, тяжесть, боль в нижней части грудной клетки справа | тошнота, рвота | снижение массы тела | расстройства стула (диарея) | отсутствие аппетита | выраженная потливость, особенно ночью | болезненность при пальпации (прощупывании) живота в области правого подреберья, в проекции абсцесса | хрипы в нижнем отделе правого легкого | пожелтение кожи, видимых слизистых оболочек, склер</t>
+  </si>
+  <si>
+    <t>0.02%</t>
+  </si>
+  <si>
+    <t>https://www.smclinic.ru/upload/iblock/622/agauxmffhkiv2ey255efrpzhbf6vuok7.jpg.webp</t>
+  </si>
+  <si>
+    <t>Ощущения слабые, фоновые</t>
+  </si>
+  <si>
+    <t>Нет явной связи</t>
+  </si>
+  <si>
+    <t>Нет боли</t>
+  </si>
+  <si>
+    <t>Стало лучше</t>
+  </si>
+  <si>
+    <t>снижение гемоглобина и эритроцитов</t>
+  </si>
+  <si>
+    <t>снижение уровня витамина А (ретинола) в сыворотке крови (&lt;0,35 мкмоль/л — острый дефицит, 0,7–1,22 мкмоль/л — начальная недостаточность) | снижение ретинол-связывающего белка (РСБ) | снижение уровня цинка</t>
+  </si>
+  <si>
+    <t>апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | сухость и покраснение кожи | истончение, ломкость и выпадение волос | кожный зуд | расслаивание и хрупкость ногтевых пластин | появление шелушений, трещин на лице и теле | снижение или полная потеря обоняния | снижение или полная потеря вкусового восприятия | приступы отвращения к еде | тошнота после приемов пищи | синдром «куриной слепоты», когда человек в сумерках или темноте очень плохо видит | нарушение фертильности | развитие анемии | развитие мочекаменной болезни | ослабление иммунитета</t>
+  </si>
+  <si>
+    <t>Основа профилактики авитаминоза – сбалансированное и рациональное питание. Необходимо отказаться от строгих диет и питаться разнообразно, включая в ежедневный рацион:
+нежирные сорта мяса и рыбы;
+молочные и кисломолочные продукты;
+твердые сыры;
+свежие плоды и зелень;
+крупы;
+морепродукты;
+яйца;
+орехи и сухофрукты;
+сливочное и растительное масло.
+Желательно максимально ограничить блюда фаст-фуда, продукты быстрого приготовления, алкоголь. Также стоит придерживаться активного образа жизни, не заниматься самолечением и регулярно проходить профилактические обследования со сдачей необходимых анализов.</t>
+  </si>
+  <si>
+    <t>https://www.smclinic.ru/upload/iblock/c90/r0yk0odmer7n8haiyf900t1j3eu3lexs.jpg.webp</t>
+  </si>
+  <si>
+    <t>Тупая/Ноющая: Часто постоянная, глубокая, трудно определить точное местоположение</t>
+  </si>
+  <si>
+    <t>снижение гемоглобина (признаки анемии в некоторых случаях) | повышение паратгормона (при тяжелом дефиците может быть косвенно связано с изменениями обмена) | нормальный уровень лейкоцитов и СОЭ (если нет сопутствующей инфекции)</t>
+  </si>
+  <si>
+    <t>снижение уровня 25-ОН витамина D (основной маркер: &lt;20 нг/мл — дефицит, 20–30 нг/мл — недостаточность) | снижение уровня кальция (в тяжелых случаях) | снижение уровня фосфатов | повышение активности щелочной фосфатазы (ЩФ)</t>
+  </si>
+  <si>
+    <t>апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | мышечные, суставные и костные боли | частые переломы, которые долго заживают | нарушения координации и походки | судороги в мышцах, особенно в ночное время | неврологические признаки | истончение эмали зубов | очаговое выпадение волос на голове и теле | ослабление иммунитета</t>
+  </si>
+  <si>
+    <t>ИМТ</t>
+  </si>
+  <si>
+    <t>≥ 30</t>
+  </si>
+  <si>
+    <t>Нервная система (головокружение, онемение)</t>
+  </si>
+  <si>
+    <t>снижение гемоглобина | снижение эритроцитов (признаки гемолитической анемии) | изменение формы эритроцитов (акантоцитоз)</t>
+  </si>
+  <si>
+    <t>снижение уровня альфа-токоферола в сыворотке крови (ниже 5 мкг/мл или соотношение витамин Е/общие липиды менее 0,8 мг/г) | повышение уровня креатинфосфокиназы (КФК) при поражении мышц</t>
+  </si>
+  <si>
+    <t>апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | снижение половой функции | мышечная слабость и судороги, особенно в руках и ногах | спазмы мышц | ослабление иммунитета</t>
+  </si>
+  <si>
+    <t>апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | регулярные самопроизвольные прерывания беременности | мышечная слабость и судороги, особенно в руках и ногах | спазмы мышц | ослабление иммунитета</t>
+  </si>
+  <si>
+    <t>50 - 100</t>
+  </si>
+  <si>
+    <t>снижение уровня тромбоцитов | возможно снижение гемоглобина и эритроцитов</t>
+  </si>
+  <si>
+    <t>снижение уровня протромбина (повышение МНО/ПТИ) | удлинение протромбинового времени и АЧТВ | снижение активности факторов свертывания II, VII, IX, X</t>
+  </si>
+  <si>
+    <t>Наличие золотистого стафилококка</t>
+  </si>
+  <si>
+    <t>апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | спонтанные кровотечения | носовые кровотечения, которые возникают на фоне физической нагрузки | носовые кровотечения, которые возникают на фоне эмоционального переживания | носовые кровотечения | легочные и желудочные кровотечения | кровоизлияния в суставные полости | даже от малейшего давления возникают многочисленные синяки на лице и теле | ослабление иммунитета</t>
+  </si>
+  <si>
+    <t>&lt; 18.5 | &gt; 30</t>
+  </si>
+  <si>
+    <t>снижение гемоглобина | снижение эритроцитов</t>
+  </si>
+  <si>
+    <t>снижение уровня аскорбиновой кислоты в плазме крови (ниже 0,2 мг/дл) | снижение уровня аскорбиновой кислоты в лейкоцитах</t>
+  </si>
+  <si>
+    <t>апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | цинга | десны сильно кровоточат | выпадение зубов | поражение сердечно-сосудистой системы и почек | кровоизлияние в мягкие ткани | ослабление иммунитета</t>
+  </si>
+  <si>
+    <t>снижение гемоглобина | снижение эритроцитов | увеличение среднего объема эритроцитов (макроцитоз) | снижение тромбоцитов | снижение лейкоцитов (при дефиците B12/B9)</t>
+  </si>
+  <si>
+    <t>снижение уровня конкретного витамина (B1, B6, B12) в сыворотке | повышение уровня гомоцистеина | повышение уровня непрямого билирубина</t>
+  </si>
+  <si>
+    <t>апатия | нарушения сна | сонливость | сниженный или чрезмерный аппетит | ослабление иммунитета | постоянная одышка | судороги в икроножных мышцах, особенно после ходьбы, бега, физических упражнений | снижение чувствительности в стопах и пальцах ног | расстройства аппетита и стула | частые головные боли | появление трещин в уголках рта | отечность, ощущения зуда и жжения на языке | снижение выносливости | головокружение | шелушение кожи на лице и теле | нарушения зрения | учащенный пульс и громкое, отчетливое сердцебиение | поражение периферическая нервная система | гепатомегалия | атрофические изменения в слизистых тканях органов пищеварения | недержание мочи и каловых масс</t>
+  </si>
+  <si>
+    <t>Юго-Восточная Азия (Таиланд, Вьетнам, Лаос) | Восточная Африка (Уганда, Эфиопия) | Южная Азия (Индия) | Развитые страны (США, Европа)</t>
+  </si>
+  <si>
+    <t>https://www.smclinic.ru/upload/iblock/a33/1pnur2suhd4b7tlyssvm0mklwtxxao01.jpg.webp</t>
+  </si>
+  <si>
+    <t>снижение уровня пролактина | возможно снижение уровня эстрогенов и тиреоидных гормонов (Т3, Т4) | изменения уровня глюкозы</t>
+  </si>
+  <si>
+    <t>Только внутренние ощущения</t>
+  </si>
+  <si>
+    <t>низкий уровень глюкозы или электролитный дисбаланс (при метаболической этиологии</t>
+  </si>
+  <si>
+    <t>Лечение агнозии направлено на восстановление нарушенного взаимодействия между восприятием и его осмыслением. Основная задача терапии — помочь мозгу заново выстроить утраченные связи, частично компенсировать дефект и снизить риск дальнейшего повреждения корковых структур. Выбор лечебной стратегии всегда индивидуален и зависит от причины возникновения расстройства, его клинической формы и общего функционального состояния пациента. На практике чаще всего применяется сочетание медикаментозных и немедикаментозных методов воздействия.
+Фармакологическая поддержка подбирается с учетом ведущих механизмов поражения и может включать следующие группы средств:
+препараты, способствующие улучшению кровоснабжения мозговой ткани и доставки кислорода;
+средства, поддерживающие энергетические и обменные процессы в нейронах;
+препараты с защитным действием в отношении нервных клеток;
+средства, влияющие на передачу сигналов между нейронами и повышающие адаптационные возможности мозга;
+противовоспалительные и противоотечные средства в случаях, когда расстройство обусловлено активным повреждающим процессом.
+Медикаментозная терапия создает благоприятный фон для восстановления функций коры и помогает замедлить развитие структурных и функциональных изменений.
+Ведущее значение в коррекции агнозии принадлежит немедикаментозным методам, направленным на активную перестройку познавательных процессов. В программу лечения могут входить:
+системная нейропсихологическая работа с акцентом на тренировку нарушенных механизмов узнавания;
+упражнения, развивающие зрительное, слуховое и тактильное восприятие;
+логопедическая коррекция при нарушениях понимания речи и звуков;
+когнитивные занятия, направленные на улучшение анализа и интерпретации информации;
+обучение адаптивным стратегиям, облегчающим повседневную деятельность;
+психотерапевтическая поддержка, помогающая снизить тревожность и повысить мотивацию к лечению.
+Комплексное воздействие позволяет задействовать компенсаторные ресурсы мозга и способствует формированию новых функциональных связей. Результативность лечения во многом определяется регулярностью занятий и активным участием самого пациента в процессе восстановления.</t>
+  </si>
+  <si>
+    <t>https://www.smclinic.ru/upload/iblock/a4e/23x2hes00rw8ore50z00t9n1huoo0orv.jpg.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">выраженное снижение или отсутствие зернистых лейкоцитов (гранулоцитов) | общее снижение уровня лейкоцитов (лейкопения) | снижение гемоглобина, эритроцитов и тромбоцитов </t>
+  </si>
+  <si>
+    <t>повышение уровня С-реактивного белка (СРБ) | возможен электролитный дисбаланс | низкий уровень глюкозы</t>
+  </si>
+  <si>
+    <t>резкое снижение защитных возможностей организма | общее состояние ухудшается в течение нескольких часов или дней | язвенно-некротические изменения слизистой оболочки полости рта | боли при глотании, иррадиирующие в уши | признаки интоксикации, не соответствующие локальным проявлениям | воспаление десен с кровоточивостью и неприятным запахом | воспалительные изменения кожи и подкожной клетчатки | боль в горле, затруднение глотания, ощущение жжения в ротоглотке | появление налетов серо-зеленого цвета на миндалинах | склонность к быстрому распространению инфекционных процессов</t>
+  </si>
+  <si>
+    <t>0.08%</t>
+  </si>
+  <si>
+    <t>https://www.smclinic.ru/upload/iblock/8b8/4bzk3k30figkctnhrv8k5xpc2ws75xew.jpg.webp</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3076,21 +3253,28 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF232323"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF0A0A0A"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3115,31 +3299,60 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3468,13 +3681,1683 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B7EB09-25FF-2F4A-A965-6C6B234C8B3A}">
+  <dimension ref="A1:AO48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.5" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="9" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="16" style="9" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="20.5" style="9" customWidth="1"/>
+    <col min="9" max="9" width="13" style="9" customWidth="1"/>
+    <col min="10" max="10" width="16.5" style="9" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="9"/>
+    <col min="12" max="12" width="13.83203125" style="9" customWidth="1"/>
+    <col min="13" max="15" width="10.83203125" style="9"/>
+    <col min="16" max="16" width="22.83203125" style="9" customWidth="1"/>
+    <col min="17" max="30" width="10.83203125" style="9"/>
+    <col min="31" max="41" width="10.83203125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC2" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="AD2" s="9" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A3" s="8">
+        <f>A2 + 1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA3" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="AB3" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="AC3" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="AD3" s="11">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
+        <f t="shared" ref="A4:A48" si="0">A3 + 1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="AA4" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="AB4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC4" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="AD4" s="9" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A5" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA5" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC5" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="AD5" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A6" s="8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V6" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="W6" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA6" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="AB6" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC6" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="AD6" s="11">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A7" s="8">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="W7" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA7" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="AB7" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC7" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="AD7" s="11">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A8" s="8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="W8" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA8" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="AB8" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC8" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="AD8" s="11">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A9" s="8">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA9" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB9" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="AD9" s="11">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A10" s="8">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V10" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="W10" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="X10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA10" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB10" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC10" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="AD10" s="11">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A11" s="8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V11" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="W11" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y11" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z11" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA11" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC11" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="AD11" s="11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A12" s="8">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="V12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="W12" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y12" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA12" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC12" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="AD12" s="11">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A13" s="8">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="U13" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="V13" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="W13" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y13" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z13" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB13" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC13" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="AD13" s="9" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A14" s="8">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="U14" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="V14" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="W14" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="X14" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z14" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA14" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB14" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC14" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="AD14" s="9" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A15" s="8">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="U15" s="7"/>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A16" s="8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="U16" s="7"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="8">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="8">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="8">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="8">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="8">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="8">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="8">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="8">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="8">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="8">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="8">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="8">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="8">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="8">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>410</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="A1:AD1048576">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A1))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="AC2" r:id="rId1" xr:uid="{BCADD7F4-C6D7-B842-A6D8-894B2CAD0C77}"/>
+    <hyperlink ref="AC3" r:id="rId2" xr:uid="{A3EBA9E5-A838-9B4F-8881-DDA1231A4233}"/>
+    <hyperlink ref="AC4" r:id="rId3" xr:uid="{161A3114-4BED-4848-BCD3-8063E0411DBB}"/>
+    <hyperlink ref="AC5" r:id="rId4" xr:uid="{DDBEFDF1-254F-FA45-8030-245EB0392B01}"/>
+    <hyperlink ref="AC6" r:id="rId5" xr:uid="{7C8AB5D1-5F2F-964A-B91A-FC5FC5A0BC3B}"/>
+    <hyperlink ref="AC8" r:id="rId6" xr:uid="{09064195-21D1-1D4B-B646-872F76D4C690}"/>
+    <hyperlink ref="AC9" r:id="rId7" xr:uid="{573B43C4-4762-244E-98CC-94D90C971AC0}"/>
+    <hyperlink ref="AC7" r:id="rId8" xr:uid="{0C4EE28D-C7C8-D34A-B187-04ECE755C4E3}"/>
+    <hyperlink ref="AC10" r:id="rId9" xr:uid="{FFD944BD-F68D-8446-A66B-535385186B6A}"/>
+    <hyperlink ref="AC11" r:id="rId10" xr:uid="{017922DB-99E2-C04B-93D0-5A8E3223FD87}"/>
+    <hyperlink ref="AC12" r:id="rId11" xr:uid="{F063B387-0CFC-1A49-9805-FE0F0315294B}"/>
+    <hyperlink ref="AC13" r:id="rId12" xr:uid="{D60AF7BA-4437-B64F-894E-EC56E40F40C5}"/>
+    <hyperlink ref="AC14" r:id="rId13" xr:uid="{F84DDBDA-790F-134B-8AF8-5AFF1EA9055A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9421AA35-C797-EB48-B98A-18AB923DBDE8}">
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.1640625" style="1" customWidth="1"/>
-    <col min="3" max="5" width="20" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20" style="1" customWidth="1"/>
+    <col min="4" max="4" width="78.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="1" customWidth="1"/>
     <col min="6" max="6" width="29.1640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="30.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="32.5" style="1" customWidth="1"/>
@@ -3482,11 +5365,11 @@
     <col min="10" max="10" width="19.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="23.5" style="1" customWidth="1"/>
     <col min="12" max="13" width="10.83203125" style="1"/>
-    <col min="14" max="14" width="10.83203125" style="3"/>
+    <col min="14" max="14" width="10.83203125" style="2"/>
     <col min="15" max="15" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="38" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="57" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3494,7 +5377,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -3506,2301 +5389,1671 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <f t="shared" ref="A3:A36" si="0">A2 + 1</f>
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="M3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <f>A2 + 1</f>
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <f t="shared" ref="A4:A48" si="0">A3 + 1</f>
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
       <c r="B16" s="1" t="s">
-        <v>143</v>
+        <v>251</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>144</v>
+        <v>253</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>147</v>
+        <v>255</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>148</v>
+        <v>256</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>149</v>
+        <v>257</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>151</v>
+        <v>260</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>153</v>
+        <v>261</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>154</v>
+        <v>262</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>155</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>156</v>
+        <v>265</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>157</v>
+        <v>266</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>160</v>
+        <v>269</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>158</v>
+        <v>267</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>159</v>
+        <v>268</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>161</v>
+        <v>270</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>162</v>
+        <v>271</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>163</v>
+        <v>272</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>165</v>
+        <v>273</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>166</v>
+        <v>275</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>167</v>
+        <v>262</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>168</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>169</v>
+        <v>277</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>173</v>
+        <v>282</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>171</v>
+        <v>278</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>172</v>
+        <v>279</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>174</v>
+        <v>281</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>175</v>
+        <v>283</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>177</v>
+        <v>285</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>180</v>
+        <v>262</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>181</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>182</v>
+        <v>289</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>183</v>
+        <v>290</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>186</v>
+        <v>293</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>184</v>
+        <v>291</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>185</v>
+        <v>292</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>187</v>
+        <v>294</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>188</v>
+        <v>295</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>189</v>
+        <v>296</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>190</v>
+        <v>297</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>193</v>
+        <v>262</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>196</v>
+        <v>302</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>197</v>
+        <v>303</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>200</v>
+        <v>306</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>203</v>
+        <v>310</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>114</v>
+        <v>311</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>205</v>
+        <v>262</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>312</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>206</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>207</v>
+        <v>314</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>211</v>
+        <v>318</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>209</v>
+        <v>316</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>210</v>
+        <v>317</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>212</v>
+        <v>319</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>213</v>
+        <v>320</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>214</v>
+        <v>321</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>215</v>
+        <v>322</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>216</v>
+        <v>32</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>217</v>
+        <v>311</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>218</v>
+        <v>262</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>323</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>219</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>220</v>
+        <v>329</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>221</v>
+        <v>336</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>224</v>
+        <v>338</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>222</v>
+        <v>335</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>223</v>
+        <v>337</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>225</v>
+        <v>339</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>226</v>
+        <v>340</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>227</v>
+        <v>341</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>228</v>
+        <v>342</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>230</v>
+        <v>343</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>231</v>
+        <v>262</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>232</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>233</v>
+        <v>330</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>234</v>
+        <v>345</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>236</v>
+        <v>348</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>235</v>
+        <v>346</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>237</v>
+        <v>347</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>238</v>
+        <v>349</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>239</v>
+        <v>350</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>240</v>
+        <v>351</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>241</v>
+        <v>353</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>242</v>
+        <v>352</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>243</v>
+        <v>262</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>244</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>245</v>
+        <v>331</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>246</v>
+        <v>356</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>249</v>
+        <v>359</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>247</v>
+        <v>357</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>248</v>
+        <v>358</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>251</v>
+        <v>360</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>255</v>
+        <v>363</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>254</v>
+        <v>364</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>256</v>
+        <v>365</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>98</v>
+        <v>262</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>257</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>245</v>
+        <v>332</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>246</v>
+        <v>368</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>250</v>
+        <v>371</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>247</v>
+        <v>369</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>248</v>
+        <v>370</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>251</v>
+        <v>372</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>252</v>
+        <v>373</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>253</v>
+        <v>374</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>255</v>
+        <v>376</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>254</v>
+        <v>375</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>256</v>
+        <v>377</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>98</v>
+        <v>262</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>257</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>258</v>
+        <v>333</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>259</v>
+        <v>379</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>261</v>
+        <v>382</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>260</v>
+        <v>380</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>39</v>
+        <v>381</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>262</v>
+        <v>383</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>263</v>
+        <v>384</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>264</v>
+        <v>385</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>265</v>
+        <v>386</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>266</v>
+        <v>387</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>267</v>
+        <v>200</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>268</v>
+        <v>50</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>269</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>271</v>
+        <v>390</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>274</v>
+        <v>393</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>272</v>
+        <v>391</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>273</v>
+        <v>392</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>275</v>
+        <v>394</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>276</v>
+        <v>395</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>277</v>
+        <v>396</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>279</v>
+        <v>397</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>278</v>
+        <v>398</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>256</v>
+        <v>399</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>205</v>
+        <v>23</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>400</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>280</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>281</v>
+        <v>402</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>283</v>
+        <v>415</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>285</v>
+        <v>412</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>282</v>
+        <v>411</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>284</v>
+        <v>32</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>286</v>
+        <v>413</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>287</v>
+        <v>32</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>288</v>
+        <v>414</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>289</v>
+        <v>32</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>291</v>
+        <v>87</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>293</v>
+        <v>262</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>294</v>
+        <v>416</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>295</v>
+        <v>403</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>296</v>
+        <v>421</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>299</v>
+        <v>419</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>297</v>
+        <v>417</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>298</v>
+        <v>418</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>301</v>
+        <v>422</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>302</v>
+        <v>423</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>304</v>
+        <v>424</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>303</v>
+        <v>425</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>305</v>
+        <v>426</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>141</v>
+        <v>262</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>306</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>310</v>
+        <v>429</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>312</v>
+        <v>431</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>308</v>
+        <v>428</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>309</v>
+        <v>430</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>311</v>
+        <v>432</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>313</v>
+        <v>433</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>314</v>
+        <v>434</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>315</v>
+        <v>435</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>316</v>
+        <v>436</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>317</v>
+        <v>426</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>141</v>
+        <v>50</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>437</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>318</v>
+        <v>438</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>319</v>
+        <v>405</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>320</v>
+        <v>441</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>323</v>
+        <v>442</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>321</v>
+        <v>439</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>322</v>
+        <v>440</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>324</v>
+        <v>443</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>325</v>
+        <v>444</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>326</v>
+        <v>445</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>327</v>
+        <v>447</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>39</v>
+        <v>446</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>328</v>
+        <v>426</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>329</v>
+        <v>262</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>448</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>330</v>
+        <v>449</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>331</v>
+        <v>406</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>332</v>
+        <v>459</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>335</v>
+        <v>452</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>333</v>
+        <v>450</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>334</v>
+        <v>451</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>336</v>
+        <v>453</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>337</v>
+        <v>454</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>338</v>
+        <v>455</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>339</v>
+        <v>457</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>341</v>
+        <v>458</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>342</v>
+        <v>262</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>343</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>345</v>
+        <v>407</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>348</v>
+        <v>463</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>346</v>
+        <v>461</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>347</v>
+        <v>462</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>349</v>
+        <v>464</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>351</v>
+        <v>466</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>39</v>
+        <v>468</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>341</v>
+        <v>469</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>353</v>
+        <v>262</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>470</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>354</v>
+        <v>471</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>368</v>
+        <v>474</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>365</v>
+        <v>472</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>367</v>
+        <v>473</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>369</v>
+        <v>475</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>370</v>
+        <v>476</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>371</v>
+        <v>477</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>372</v>
+        <v>478</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>39</v>
+        <v>479</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>373</v>
+        <v>480</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>293</v>
+        <v>262</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>470</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>374</v>
+        <v>481</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>360</v>
+        <v>409</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>375</v>
+        <v>490</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>378</v>
+        <v>484</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>376</v>
+        <v>482</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>377</v>
+        <v>483</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>379</v>
+        <v>485</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>380</v>
+        <v>486</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>381</v>
+        <v>487</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>383</v>
+        <v>488</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>382</v>
+        <v>489</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>384</v>
+        <v>480</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>90</v>
+        <v>262</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>491</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>385</v>
+        <v>492</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>361</v>
+        <v>410</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>386</v>
+        <v>493</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>389</v>
+        <v>495</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>387</v>
+        <v>494</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>390</v>
+        <v>496</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>391</v>
+        <v>497</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>392</v>
+        <v>498</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>393</v>
+        <v>499</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>394</v>
+        <v>500</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>395</v>
+        <v>501</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>396</v>
+        <v>262</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>491</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A43" s="1">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A44" s="1">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A45" s="1">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A46" s="1">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E46" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="O46" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A47" s="1">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A48" s="1">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="O48" s="1" t="s">
-        <v>532</v>
-      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="P2" r:id="rId1" xr:uid="{CF71BBC1-C361-B04C-8EE0-74236E89983D}"/>
-    <hyperlink ref="P3" r:id="rId2" xr:uid="{ED3922B6-7AEF-EB4A-9FCC-7F77BF01BB7E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{468C5F06-8BE1-0F45-9BB4-7D65D0D0C785}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5811,18 +7064,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>355</v>
+        <v>325</v>
       </c>
       <c r="B1" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="B2" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
